--- a/requests.xlsx
+++ b/requests.xlsx
@@ -1,34 +1,130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Acoole_Portal\backups\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A13972-4258-4155-A5A9-02338124785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Transaction Type</t>
+  </si>
+  <si>
+    <t>Category Reason</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Amount (£)</t>
+  </si>
+  <si>
+    <t>Line Manager</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Attachment Name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Director Comments</t>
+  </si>
+  <si>
+    <t>Decision Date</t>
+  </si>
+  <si>
+    <t>Decision By</t>
+  </si>
+  <si>
+    <t>PDF File Path</t>
+  </si>
+  <si>
+    <t>Edited From ID</t>
+  </si>
+  <si>
+    <t>Old Data</t>
+  </si>
+  <si>
+    <t>Aston</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>GYM Membership</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Neil Jackson</t>
+  </si>
+  <si>
+    <t>GYM Membership August 2026</t>
+  </si>
+  <si>
+    <t>ID_1_EDIT_F1_Aston Whyke.png</t>
+  </si>
+  <si>
+    <t>approved</t>
+  </si>
+  <si>
+    <t>2026-09-01 15:50</t>
+  </si>
+  <si>
+    <t>Andy Coole</t>
+  </si>
+  <si>
+    <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +143,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,174 +445,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Transaction Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category Reason</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Line Manager</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Attachment Name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Director Comments</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Decision Date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Decision By</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>PDF File Path</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Edited From ID</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Old Data</t>
-        </is>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aston</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Addition</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GYM Membership</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
         <v>27.99</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Neil Jackson</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>GYM Membership August 2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ID_1_EDIT_F1_Aston Whyke.png</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-09-01 15:50</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Andy Coole</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>C:\Users\WaisRahimi\Desktop\MyOfficeApp\approved_pdfs\Aston - GYM Membership - £28.99 - 2026-09-01.pdf</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
-        </is>
+      <c r="H2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/requests.xlsx
+++ b/requests.xlsx
@@ -1,130 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Acoole_Portal\backups\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A13972-4258-4155-A5A9-02338124785D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Transaction Type</t>
-  </si>
-  <si>
-    <t>Category Reason</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Amount (£)</t>
-  </si>
-  <si>
-    <t>Line Manager</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Attachment Name</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Director Comments</t>
-  </si>
-  <si>
-    <t>Decision Date</t>
-  </si>
-  <si>
-    <t>Decision By</t>
-  </si>
-  <si>
-    <t>PDF File Path</t>
-  </si>
-  <si>
-    <t>Edited From ID</t>
-  </si>
-  <si>
-    <t>Old Data</t>
-  </si>
-  <si>
-    <t>Aston</t>
-  </si>
-  <si>
-    <t>Accounts</t>
-  </si>
-  <si>
-    <t>Addition</t>
-  </si>
-  <si>
-    <t>GYM Membership</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>Neil Jackson</t>
-  </si>
-  <si>
-    <t>GYM Membership August 2026</t>
-  </si>
-  <si>
-    <t>ID_1_EDIT_F1_Aston Whyke.png</t>
-  </si>
-  <si>
-    <t>approved</t>
-  </si>
-  <si>
-    <t>2026-09-01 15:50</t>
-  </si>
-  <si>
-    <t>Andy Coole</t>
-  </si>
-  <si>
-    <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -445,105 +408,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category Reason</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Amount (£)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Line Manager</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Attachment Name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Director Comments</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Decision Date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Decision By</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PDF File Path</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Edited From ID</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Old Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aston</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GYM Membership</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>27.99</v>
       </c>
-      <c r="H2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>28</v>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Neil Jackson</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>GYM Membership August 2026</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ID_1_EDIT_F1_Aston Whyke.png</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-01 15:50</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Andy Coole</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/requests.xlsx
+++ b/requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,73 @@
           <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wais Rahimi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GYM Membership</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Millie</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Gym</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ID_2_F1_IMG_1803.jpeg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:47:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Andy Coole</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/requests.xlsx
+++ b/requests.xlsx
@@ -1,34 +1,94 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WaisRahimi\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D354625C-B708-4D1C-A4A9-F91116456F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Transaction Type</t>
+  </si>
+  <si>
+    <t>Category Reason</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Amount (£)</t>
+  </si>
+  <si>
+    <t>Line Manager</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Attachment Name</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Director Comments</t>
+  </si>
+  <si>
+    <t>Decision Date</t>
+  </si>
+  <si>
+    <t>Decision By</t>
+  </si>
+  <si>
+    <t>PDF File Path</t>
+  </si>
+  <si>
+    <t>Edited From ID</t>
+  </si>
+  <si>
+    <t>Old Data</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +107,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,238 +409,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Employee Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Department</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Transaction Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Category Reason</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Amount (£)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Line Manager</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Attachment Name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Director Comments</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Decision Date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Decision By</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>PDF File Path</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Edited From ID</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Old Data</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Aston</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Addition</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GYM Membership</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Neil Jackson</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>GYM Membership August 2026</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ID_1_EDIT_F1_Aston Whyke.png</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-09-01 15:50</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Andy Coole</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>{'emp_name': 'Aston', 'dept': 'Accounts', 'type': 'Addition', 'category': 'GYM Membership', 'date': '2026-09-01', 'amount': 28.99, 'manager': 'Neil Jackson', 'desc': 'GYM Membership August 2026'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Wais Rahimi</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Accounts</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Addition</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GYM Membership</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-09-06</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Millie</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Gym</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ID_2_F1_IMG_1803.jpeg</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>approved</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-09-06 11:47:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Andy Coole</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/requests.xlsx
+++ b/requests.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WaisRahimi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WaisRahimi\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D354625C-B708-4D1C-A4A9-F91116456F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04F4FD4F-B58A-427F-A506-73F1197C0907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/requests.xlsx
+++ b/requests.xlsx
@@ -1,94 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WaisRahimi\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{04F4FD4F-B58A-427F-A506-73F1197C0907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Department</t>
-  </si>
-  <si>
-    <t>Transaction Type</t>
-  </si>
-  <si>
-    <t>Category Reason</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Amount (£)</t>
-  </si>
-  <si>
-    <t>Line Manager</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Attachment Name</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Director Comments</t>
-  </si>
-  <si>
-    <t>Decision Date</t>
-  </si>
-  <si>
-    <t>Decision By</t>
-  </si>
-  <si>
-    <t>PDF File Path</t>
-  </si>
-  <si>
-    <t>Edited From ID</t>
-  </si>
-  <si>
-    <t>Old Data</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -107,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -409,61 +408,655 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Employee Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category Reason</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Amount (£)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Line Manager</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Attachment Name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Director Comments</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Decision Date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Decision By</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>PDF File Path</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Edited From ID</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Old Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GYM Membership</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Millie</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ID_1_EDIT_F1_Logo-2.png</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-09-08 20:12:52</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>{"emp_name": "Karen", "dept": "Accounts", "type": "Addition", "category": "GYM Membership", "date": "2026-09-08", "amount": 34.0, "manager": "Millie", "desc": "Test"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Karen</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Food Allowance</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Millie</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GYME</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ID_2_F1_GYM Membership.jpg, ID_2_EDIT_F2_Roblox gammer.jpeg</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2026-09-08 20:12:45</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>{"emp_name": "Karen", "dept": "Accounts", "type": "Addition", "category": "Food Allowance", "date": "2026-09-08", "amount": 33.0, "manager": "Millie", "desc": "GYME"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aston</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GYM Membership</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ID_3_F1_Roblox gammer.jpeg</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:35:58</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>karen</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Food Allowance</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>er</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ID_4_F1_GYM Membership.jpg</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:35:54</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Isolator</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Food Allowance</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>32</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ID_5_F1_Roblox gammer.jpeg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:35:51</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Neil</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GYM Membership</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>34</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Kerry</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ID_6_F1_London.jpg</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-09 07:35:47</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Food Allowance</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Millie</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ID_7_EDIT_F1_London.jpg</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-09 22:12:13</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{"emp_name": "Hannah", "dept": "Accounts", "type": "Addition", "category": "Food Allowance", "date": "2026-09-09", "amount": 36.0, "manager": "Millie", "desc": "Food"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jack Dun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Accounts</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Addition</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Food Allowance</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Meal Allowance</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ID_8_F1_GYM Membership.png, ID_8_EDIT_F2_Screenshot 2026-06-11 081946.png</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>approved</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>[2026-09-10 09:57] ✅ Changed to Approved by Andy Acoole:</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:57:41</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Andy Acoole</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{"emp_name": "Jack Dun", "dept": "Accounts", "type": "Addition", "category": "Food Allowance", "date": "2026-09-10", "amount": 75.0, "manager": "Angela", "desc": "Meal Allowance"}</t>
+        </is>
       </c>
     </row>
   </sheetData>
